--- a/excel-calculation/excel-model/S&R_stochastic.xlsx
+++ b/excel-calculation/excel-model/S&R_stochastic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WiN\Desktop\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\excel-calculation\excel-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133EDAAF-93AB-4ADD-A75B-B1E5010CEFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0028568-8FE5-45B6-B70B-759FCEC83F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="15306" windowHeight="8952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S&amp;R Stochastic" sheetId="4" r:id="rId1"/>
@@ -352,25 +352,25 @@
     <t>Close</t>
   </si>
   <si>
-    <t>Peak_Line_1</t>
-  </si>
-  <si>
-    <t>Peak_Line_2</t>
-  </si>
-  <si>
-    <t>Peak_Line_3</t>
-  </si>
-  <si>
-    <t>Bottom_Line_1</t>
-  </si>
-  <si>
-    <t>Bottom_Line_2</t>
-  </si>
-  <si>
-    <t>Bottom_Line_3</t>
-  </si>
-  <si>
-    <t>Trendline Stochastic</t>
+    <t>horiz_peak_line_1</t>
+  </si>
+  <si>
+    <t>horiz_peak_line_2</t>
+  </si>
+  <si>
+    <t>horiz_peak_line_3</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_1</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_2</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_3</t>
+  </si>
+  <si>
+    <t>trend_stoch</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -884,6 +884,9 @@
     </xf>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1298,22 +1301,22 @@
       <c r="E4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L4" s="2" t="s">
@@ -1355,7 +1358,7 @@
         <v>152.768</v>
       </c>
       <c r="L5" s="4">
-        <f t="shared" ref="L5:L36" si="0">((E5-MIN(F5:K5))/(MAX(F5:K5)-MIN(F5:K5)))</f>
+        <f>((E5-MIN(F5:K5))/(MAX(F5:K5)-MIN(F5:K5)))</f>
         <v>0.96905766526020842</v>
       </c>
     </row>
@@ -1394,7 +1397,7 @@
         <v>152.77000000000001</v>
       </c>
       <c r="L6" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L5:L36" si="0">((E6-MIN(F6:K6))/(MAX(F6:K6)-MIN(F6:K6)))</f>
         <v>0.89689265536722085</v>
       </c>
     </row>
@@ -5099,7 +5102,7 @@
         <v>152.91999999999999</v>
       </c>
       <c r="L101" s="4">
-        <f t="shared" ref="L101:L132" si="3">((E101-MIN(F101:K101))/(MAX(F101:K101)-MIN(F101:K101)))</f>
+        <f t="shared" ref="L101:L103" si="3">((E101-MIN(F101:K101))/(MAX(F101:K101)-MIN(F101:K101)))</f>
         <v>0.20864661654138381</v>
       </c>
     </row>
